--- a/tia_exports/0_25_40_1/PLCTags.xlsx
+++ b/tia_exports/0_25_40_1/PLCTags.xlsx
@@ -2,8 +2,8 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Constants" sheetId="1" r:id="Rbd1add3cf2cb4d54"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="TagTable Properties" sheetId="2" r:id="R8250e1cbef16444f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Constants" sheetId="1" r:id="R76d1874b9c0b4f45"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="TagTable Properties" sheetId="2" r:id="Rc01ebfa34a954ee5"/>
   </x:sheets>
 </x:workbook>
 </file>
